--- a/data/Articoli.xlsx
+++ b/data/Articoli.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Estrazione_DB_CAD\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moltenicspa-my.sharepoint.com/personal/pfrapoli_unifor_it/Documents/Documenti/GitHub/Estrazione_DB_CAD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B75037-8D58-494E-ADE8-B2D3E345435F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{D4B75037-8D58-494E-ADE8-B2D3E345435F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05B801ED-770D-4402-88EE-843FEEFCB358}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6670C9F1-34F6-47C3-9A3D-147FE61E4AEA}"/>
+    <workbookView xWindow="4575" yWindow="1260" windowWidth="25335" windowHeight="12945" xr2:uid="{6670C9F1-34F6-47C3-9A3D-147FE61E4AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="837">
   <si>
     <t>SISTEMA</t>
   </si>
@@ -2042,15 +2042,6 @@
     <t>5RAVWCD000</t>
   </si>
   <si>
-    <t>5RBTRA00CC</t>
-  </si>
-  <si>
-    <t>5RBTRB00CC</t>
-  </si>
-  <si>
-    <t>5RBTRC00CC</t>
-  </si>
-  <si>
     <t>images/5R0VPQ0.png</t>
   </si>
   <si>
@@ -2271,6 +2262,294 @@
   </si>
   <si>
     <t>5RDHBA0000</t>
+  </si>
+  <si>
+    <t>5RAVPJBCQ0</t>
+  </si>
+  <si>
+    <t>5RAVPJBCQ000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 55 - JB: verticale porta lato cerniera con Q prof</t>
+  </si>
+  <si>
+    <t>5RBTRA0000</t>
+  </si>
+  <si>
+    <t>5RBTRB0000</t>
+  </si>
+  <si>
+    <t>5RBTRC0000</t>
+  </si>
+  <si>
+    <t>5RBVMQA</t>
+  </si>
+  <si>
+    <t>5RBVMQA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - Palo tecnico 58x58 con profilo in linea 66</t>
+  </si>
+  <si>
+    <t>5RBVPJBBKA</t>
+  </si>
+  <si>
+    <t>5RBVPJBBKA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato battuta con K125</t>
+  </si>
+  <si>
+    <t>5RBVPJBBKB</t>
+  </si>
+  <si>
+    <t>5RBVPJBBKB000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato battuta con K175</t>
+  </si>
+  <si>
+    <t>5RBVPJBBKC</t>
+  </si>
+  <si>
+    <t>5RBVPJBBKC000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato battuta con K279</t>
+  </si>
+  <si>
+    <t>5RBVPJBBQ0</t>
+  </si>
+  <si>
+    <t>5RBVPJBBQ000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato battuta con palo Q prof</t>
+  </si>
+  <si>
+    <t>5RBVPJBCKA</t>
+  </si>
+  <si>
+    <t>5RBVPJBCKA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato cerniera con K125</t>
+  </si>
+  <si>
+    <t>5RBVPJBCKB</t>
+  </si>
+  <si>
+    <t>5RBVPJBCKB000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato cerniera con K175</t>
+  </si>
+  <si>
+    <t>5RBVPJBCKC</t>
+  </si>
+  <si>
+    <t>5RBVPJBCKC000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato cerniera con K279</t>
+  </si>
+  <si>
+    <t>5RBVPJBCQ0</t>
+  </si>
+  <si>
+    <t>5RBVPJBCQ000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JB: verticale porta lato cerniera con Q prof</t>
+  </si>
+  <si>
+    <t>5RBVPJFBKA</t>
+  </si>
+  <si>
+    <t>5RBVPJFBKA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JF: verticale porta lato battuta con K125</t>
+  </si>
+  <si>
+    <t>5RBVPJFBKB</t>
+  </si>
+  <si>
+    <t>5RBVPJFBKB000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JF: verticale porta lato battuta con K175</t>
+  </si>
+  <si>
+    <t>5RBVPJFBKC</t>
+  </si>
+  <si>
+    <t>5RBVPJFBKC000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JF: verticale porta lato battuta con K279</t>
+  </si>
+  <si>
+    <t>5RBVPJFCKA</t>
+  </si>
+  <si>
+    <t>5RBVPJFCKA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JF: verticale porta lato cerniera con K125</t>
+  </si>
+  <si>
+    <t>5RBVPJFCKB</t>
+  </si>
+  <si>
+    <t>5RBVPJFCKB000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JF: verticale porta lato cerniera con K175</t>
+  </si>
+  <si>
+    <t>5RBVPJFCKC</t>
+  </si>
+  <si>
+    <t>5RBVPJFCKC000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JF: verticale porta lato cerniera con K279</t>
+  </si>
+  <si>
+    <t>5RBVPJSBKA</t>
+  </si>
+  <si>
+    <t>5RBVPJSBKA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JS: verticale porta lato battuta K125</t>
+  </si>
+  <si>
+    <t>5RBVPJSBKB</t>
+  </si>
+  <si>
+    <t>5RBVPJSBKB000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JS: verticale porta lato battuta K175</t>
+  </si>
+  <si>
+    <t>5RBVPJSBKC</t>
+  </si>
+  <si>
+    <t>5RBVPJSBKC000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JS: verticale porta lato battuta K279</t>
+  </si>
+  <si>
+    <t>5RBVPJSPKA</t>
+  </si>
+  <si>
+    <t>5RBVPJSPKA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JS: verticale porta lato scorrimento K125</t>
+  </si>
+  <si>
+    <t>5RBVPJSPKB</t>
+  </si>
+  <si>
+    <t>5RBVPJSPKB000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JS: verticale porta lato scorrimento K175</t>
+  </si>
+  <si>
+    <t>5RBVPJSPKC</t>
+  </si>
+  <si>
+    <t>5RBVPJSPKC000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - JS: verticale porta lato scorrimento K279</t>
+  </si>
+  <si>
+    <t>M2C</t>
+  </si>
+  <si>
+    <t>5RBVM2CA</t>
+  </si>
+  <si>
+    <t>5RBVM2CA000</t>
+  </si>
+  <si>
+    <t>Parete RP singolo vetro 66 - Montante duevie con attacco a cartongesso</t>
+  </si>
+  <si>
+    <t>images/5RAVPJBCQ0.png</t>
+  </si>
+  <si>
+    <t>images/5RBVMQA.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBBKA.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBBKB.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBBKC.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBBQ0.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBCKA.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBCKB.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBCKC.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJBCQ0.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJFBKA.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJFBKB.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJFBKC.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJFCKA.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJFCKB.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJFCKC.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJSBKA.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJSBKB.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJSBKC.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJSPKA.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJSPKB.png</t>
+  </si>
+  <si>
+    <t>images/5RBVPJSPKC.png</t>
+  </si>
+  <si>
+    <t>images/5RBVM2CA.png</t>
   </si>
 </sst>
 </file>
@@ -2642,15 +2921,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64EB9B43-EC38-40E6-B077-6084574AF46A}">
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="102.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -3085,16 +3363,16 @@
         <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F17" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="G17" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="H17" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3111,16 +3389,16 @@
         <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F18" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G18" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="H18" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3140,7 +3418,7 @@
         <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="G19" t="s">
         <v>67</v>
@@ -3172,7 +3450,7 @@
         <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3296,7 +3574,7 @@
         <v>135</v>
       </c>
       <c r="F25" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="G25" t="s">
         <v>136</v>
@@ -3322,7 +3600,7 @@
         <v>137</v>
       </c>
       <c r="F26" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G26" t="s">
         <v>138</v>
@@ -3348,7 +3626,7 @@
         <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="G27" t="s">
         <v>140</v>
@@ -3374,7 +3652,7 @@
         <v>141</v>
       </c>
       <c r="F28" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G28" t="s">
         <v>142</v>
@@ -3400,7 +3678,7 @@
         <v>143</v>
       </c>
       <c r="F29" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G29" t="s">
         <v>144</v>
@@ -3426,7 +3704,7 @@
         <v>145</v>
       </c>
       <c r="F30" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="G30" t="s">
         <v>146</v>
@@ -3452,7 +3730,7 @@
         <v>147</v>
       </c>
       <c r="F31" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G31" t="s">
         <v>148</v>
@@ -3478,7 +3756,7 @@
         <v>149</v>
       </c>
       <c r="F32" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="G32" t="s">
         <v>150</v>
@@ -3556,13 +3834,13 @@
         <v>594</v>
       </c>
       <c r="F35" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="G35" t="s">
         <v>158</v>
       </c>
       <c r="H35" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3582,13 +3860,13 @@
         <v>595</v>
       </c>
       <c r="F36" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G36" t="s">
         <v>159</v>
       </c>
       <c r="H36" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3848,7 +4126,7 @@
         <v>605</v>
       </c>
       <c r="H46" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3874,7 +4152,7 @@
         <v>608</v>
       </c>
       <c r="H47" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -3900,7 +4178,7 @@
         <v>611</v>
       </c>
       <c r="H48" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -3926,7 +4204,7 @@
         <v>614</v>
       </c>
       <c r="H49" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -3978,7 +4256,7 @@
         <v>617</v>
       </c>
       <c r="H51" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4004,7 +4282,7 @@
         <v>620</v>
       </c>
       <c r="H52" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -4030,7 +4308,7 @@
         <v>623</v>
       </c>
       <c r="H53" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4047,16 +4325,16 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>179</v>
+        <v>741</v>
       </c>
       <c r="F54" t="s">
-        <v>586</v>
+        <v>742</v>
       </c>
       <c r="G54" t="s">
-        <v>180</v>
+        <v>743</v>
       </c>
       <c r="H54" t="s">
-        <v>489</v>
+        <v>814</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4073,16 +4351,16 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>624</v>
+        <v>179</v>
       </c>
       <c r="F55" t="s">
-        <v>625</v>
+        <v>586</v>
       </c>
       <c r="G55" t="s">
-        <v>626</v>
+        <v>180</v>
       </c>
       <c r="H55" t="s">
-        <v>680</v>
+        <v>489</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4099,16 +4377,16 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F56" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="G56" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="H56" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4125,16 +4403,16 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F57" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G57" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H57" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4151,16 +4429,16 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>181</v>
+        <v>630</v>
       </c>
       <c r="F58" t="s">
-        <v>587</v>
+        <v>631</v>
       </c>
       <c r="G58" t="s">
-        <v>182</v>
+        <v>632</v>
       </c>
       <c r="H58" t="s">
-        <v>490</v>
+        <v>679</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4177,16 +4455,16 @@
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>633</v>
+        <v>181</v>
       </c>
       <c r="F59" t="s">
-        <v>634</v>
+        <v>587</v>
       </c>
       <c r="G59" t="s">
-        <v>635</v>
+        <v>182</v>
       </c>
       <c r="H59" t="s">
-        <v>683</v>
+        <v>490</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4203,16 +4481,16 @@
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F60" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G60" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H60" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4229,16 +4507,16 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F61" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="G61" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H61" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4255,16 +4533,16 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>183</v>
+        <v>639</v>
       </c>
       <c r="F62" t="s">
-        <v>588</v>
+        <v>640</v>
       </c>
       <c r="G62" t="s">
-        <v>184</v>
+        <v>641</v>
       </c>
       <c r="H62" t="s">
-        <v>491</v>
+        <v>682</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4281,16 +4559,16 @@
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>642</v>
+        <v>183</v>
       </c>
       <c r="F63" t="s">
-        <v>643</v>
+        <v>588</v>
       </c>
       <c r="G63" t="s">
-        <v>644</v>
+        <v>184</v>
       </c>
       <c r="H63" t="s">
-        <v>686</v>
+        <v>491</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4307,16 +4585,16 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F64" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="G64" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="H64" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4333,16 +4611,16 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F65" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="G65" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="H65" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4359,16 +4637,16 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>185</v>
+        <v>648</v>
       </c>
       <c r="F66" t="s">
-        <v>589</v>
+        <v>649</v>
       </c>
       <c r="G66" t="s">
-        <v>186</v>
+        <v>650</v>
       </c>
       <c r="H66" t="s">
-        <v>492</v>
+        <v>685</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4385,16 +4663,16 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>651</v>
+        <v>185</v>
       </c>
       <c r="F67" t="s">
-        <v>652</v>
+        <v>589</v>
       </c>
       <c r="G67" t="s">
-        <v>653</v>
+        <v>186</v>
       </c>
       <c r="H67" t="s">
-        <v>689</v>
+        <v>492</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4411,16 +4689,16 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F68" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G68" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H68" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4437,16 +4715,16 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F69" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G69" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="H69" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4460,19 +4738,19 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>187</v>
+        <v>657</v>
       </c>
       <c r="F70" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G70" t="s">
-        <v>188</v>
+        <v>659</v>
       </c>
       <c r="H70" t="s">
-        <v>493</v>
+        <v>688</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -4489,16 +4767,16 @@
         <v>72</v>
       </c>
       <c r="E71" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F71" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G71" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H71" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -4515,16 +4793,16 @@
         <v>72</v>
       </c>
       <c r="E72" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F72" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G72" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H72" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -4538,19 +4816,19 @@
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="E73" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F73" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G73" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H73" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -4567,16 +4845,16 @@
         <v>151</v>
       </c>
       <c r="E74" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F74" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G74" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H74" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -4593,16 +4871,16 @@
         <v>151</v>
       </c>
       <c r="E75" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F75" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H75" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -4619,16 +4897,16 @@
         <v>151</v>
       </c>
       <c r="E76" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F76" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G76" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H76" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -4636,25 +4914,25 @@
         <v>397</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="E77" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F77" t="s">
-        <v>729</v>
+        <v>666</v>
       </c>
       <c r="G77" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H77" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -4671,16 +4949,16 @@
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F78" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G78" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H78" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -4697,16 +4975,16 @@
         <v>11</v>
       </c>
       <c r="E79" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F79" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G79" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H79" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -4723,16 +5001,16 @@
         <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F80" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G80" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H80" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -4746,19 +5024,19 @@
         <v>7</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E81" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F81" t="s">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="G81" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H81" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -4775,16 +5053,16 @@
         <v>8</v>
       </c>
       <c r="E82" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F82" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="G82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H82" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -4801,16 +5079,16 @@
         <v>8</v>
       </c>
       <c r="E83" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F83" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="G83" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H83" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -4827,16 +5105,16 @@
         <v>8</v>
       </c>
       <c r="E84" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F84" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G84" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H84" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -4853,16 +5131,16 @@
         <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F85" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="G85" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H85" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -4879,16 +5157,16 @@
         <v>8</v>
       </c>
       <c r="E86" t="s">
-        <v>402</v>
+        <v>218</v>
       </c>
       <c r="F86" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="G86" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="H86" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -4905,16 +5183,16 @@
         <v>8</v>
       </c>
       <c r="E87" t="s">
-        <v>220</v>
+        <v>402</v>
       </c>
       <c r="F87" t="s">
-        <v>221</v>
+        <v>704</v>
       </c>
       <c r="G87" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H87" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -4931,16 +5209,16 @@
         <v>8</v>
       </c>
       <c r="E88" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F88" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G88" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H88" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -4957,16 +5235,16 @@
         <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F89" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G89" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H89" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -4980,19 +5258,19 @@
         <v>7</v>
       </c>
       <c r="D90" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F90" t="s">
-        <v>733</v>
+        <v>227</v>
       </c>
       <c r="G90" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H90" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -5006,19 +5284,19 @@
         <v>7</v>
       </c>
       <c r="D91" t="s">
-        <v>232</v>
+        <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>403</v>
+        <v>230</v>
       </c>
       <c r="F91" t="s">
-        <v>404</v>
+        <v>730</v>
       </c>
       <c r="G91" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H91" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -5032,19 +5310,19 @@
         <v>7</v>
       </c>
       <c r="D92" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="E92" t="s">
-        <v>234</v>
+        <v>403</v>
       </c>
       <c r="F92" t="s">
-        <v>734</v>
+        <v>404</v>
       </c>
       <c r="G92" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H92" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -5055,22 +5333,22 @@
         <v>201</v>
       </c>
       <c r="C93" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D93" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E93" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F93" t="s">
-        <v>667</v>
+        <v>731</v>
       </c>
       <c r="G93" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H93" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -5084,19 +5362,19 @@
         <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F94" t="s">
-        <v>668</v>
+        <v>744</v>
       </c>
       <c r="G94" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H94" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -5110,19 +5388,19 @@
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F95" t="s">
-        <v>669</v>
+        <v>745</v>
       </c>
       <c r="G95" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H95" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -5133,22 +5411,22 @@
         <v>201</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E96" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F96" t="s">
-        <v>243</v>
+        <v>746</v>
       </c>
       <c r="G96" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H96" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -5165,16 +5443,16 @@
         <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F97" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G97" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H97" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -5191,16 +5469,16 @@
         <v>15</v>
       </c>
       <c r="E98" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F98" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G98" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H98" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -5214,19 +5492,19 @@
         <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F99" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G99" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H99" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -5240,19 +5518,19 @@
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F100" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G100" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H100" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -5266,19 +5544,19 @@
         <v>14</v>
       </c>
       <c r="D101" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E101" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F101" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G101" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H101" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -5292,19 +5570,19 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="E102" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F102" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G102" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H102" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -5318,19 +5596,19 @@
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="E103" t="s">
-        <v>263</v>
+        <v>747</v>
       </c>
       <c r="F103" t="s">
-        <v>264</v>
+        <v>748</v>
       </c>
       <c r="G103" t="s">
-        <v>265</v>
+        <v>749</v>
       </c>
       <c r="H103" t="s">
-        <v>526</v>
+        <v>815</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -5344,19 +5622,19 @@
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E104" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F104" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G104" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H104" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -5370,19 +5648,19 @@
         <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E105" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="F105" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G105" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H105" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -5399,16 +5677,16 @@
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F106" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G106" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="H106" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -5425,16 +5703,16 @@
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F107" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G107" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="H107" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -5451,16 +5729,16 @@
         <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F108" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G108" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H108" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -5477,16 +5755,16 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>281</v>
+        <v>750</v>
       </c>
       <c r="F109" t="s">
-        <v>282</v>
+        <v>751</v>
       </c>
       <c r="G109" t="s">
-        <v>283</v>
+        <v>752</v>
       </c>
       <c r="H109" t="s">
-        <v>532</v>
+        <v>816</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -5503,16 +5781,16 @@
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>284</v>
+        <v>753</v>
       </c>
       <c r="F110" t="s">
-        <v>285</v>
+        <v>754</v>
       </c>
       <c r="G110" t="s">
-        <v>286</v>
+        <v>755</v>
       </c>
       <c r="H110" t="s">
-        <v>533</v>
+        <v>817</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -5529,16 +5807,16 @@
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>287</v>
+        <v>756</v>
       </c>
       <c r="F111" t="s">
-        <v>288</v>
+        <v>757</v>
       </c>
       <c r="G111" t="s">
-        <v>289</v>
+        <v>758</v>
       </c>
       <c r="H111" t="s">
-        <v>534</v>
+        <v>818</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -5555,16 +5833,16 @@
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>290</v>
+        <v>759</v>
       </c>
       <c r="F112" t="s">
-        <v>291</v>
+        <v>760</v>
       </c>
       <c r="G112" t="s">
-        <v>292</v>
+        <v>761</v>
       </c>
       <c r="H112" t="s">
-        <v>535</v>
+        <v>819</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -5581,16 +5859,16 @@
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="F113" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="G113" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="H113" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -5604,19 +5882,19 @@
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>296</v>
+        <v>762</v>
       </c>
       <c r="F114" t="s">
-        <v>297</v>
+        <v>763</v>
       </c>
       <c r="G114" t="s">
-        <v>298</v>
+        <v>764</v>
       </c>
       <c r="H114" t="s">
-        <v>537</v>
+        <v>820</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -5630,19 +5908,19 @@
         <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>299</v>
+        <v>765</v>
       </c>
       <c r="F115" t="s">
-        <v>300</v>
+        <v>766</v>
       </c>
       <c r="G115" t="s">
-        <v>301</v>
+        <v>767</v>
       </c>
       <c r="H115" t="s">
-        <v>538</v>
+        <v>821</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -5656,19 +5934,19 @@
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>302</v>
+        <v>768</v>
       </c>
       <c r="F116" t="s">
-        <v>303</v>
+        <v>769</v>
       </c>
       <c r="G116" t="s">
-        <v>304</v>
+        <v>770</v>
       </c>
       <c r="H116" t="s">
-        <v>539</v>
+        <v>822</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -5682,19 +5960,19 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>305</v>
+        <v>771</v>
       </c>
       <c r="F117" t="s">
-        <v>306</v>
+        <v>772</v>
       </c>
       <c r="G117" t="s">
-        <v>307</v>
+        <v>773</v>
       </c>
       <c r="H117" t="s">
-        <v>540</v>
+        <v>823</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -5708,19 +5986,19 @@
         <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="F118" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="G118" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="H118" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -5728,25 +6006,25 @@
         <v>397</v>
       </c>
       <c r="B119" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C119" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D119" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>312</v>
+        <v>774</v>
       </c>
       <c r="F119" t="s">
-        <v>735</v>
+        <v>775</v>
       </c>
       <c r="G119" t="s">
-        <v>313</v>
+        <v>776</v>
       </c>
       <c r="H119" t="s">
-        <v>542</v>
+        <v>824</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -5754,25 +6032,25 @@
         <v>397</v>
       </c>
       <c r="B120" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C120" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>314</v>
+        <v>777</v>
       </c>
       <c r="F120" t="s">
-        <v>736</v>
+        <v>778</v>
       </c>
       <c r="G120" t="s">
-        <v>315</v>
+        <v>779</v>
       </c>
       <c r="H120" t="s">
-        <v>543</v>
+        <v>825</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -5780,25 +6058,25 @@
         <v>397</v>
       </c>
       <c r="B121" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C121" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D121" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>316</v>
+        <v>780</v>
       </c>
       <c r="F121" t="s">
-        <v>708</v>
+        <v>781</v>
       </c>
       <c r="G121" t="s">
-        <v>317</v>
+        <v>782</v>
       </c>
       <c r="H121" t="s">
-        <v>544</v>
+        <v>826</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -5806,25 +6084,25 @@
         <v>397</v>
       </c>
       <c r="B122" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C122" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E122" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="F122" t="s">
-        <v>709</v>
+        <v>282</v>
       </c>
       <c r="G122" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="H122" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -5832,25 +6110,25 @@
         <v>397</v>
       </c>
       <c r="B123" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C123" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D123" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>320</v>
+        <v>783</v>
       </c>
       <c r="F123" t="s">
-        <v>710</v>
+        <v>784</v>
       </c>
       <c r="G123" t="s">
-        <v>321</v>
+        <v>785</v>
       </c>
       <c r="H123" t="s">
-        <v>546</v>
+        <v>827</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -5858,25 +6136,25 @@
         <v>397</v>
       </c>
       <c r="B124" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C124" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>322</v>
+        <v>786</v>
       </c>
       <c r="F124" t="s">
-        <v>711</v>
+        <v>787</v>
       </c>
       <c r="G124" t="s">
-        <v>323</v>
+        <v>788</v>
       </c>
       <c r="H124" t="s">
-        <v>547</v>
+        <v>828</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -5884,25 +6162,25 @@
         <v>397</v>
       </c>
       <c r="B125" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C125" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>324</v>
+        <v>789</v>
       </c>
       <c r="F125" t="s">
-        <v>712</v>
+        <v>790</v>
       </c>
       <c r="G125" t="s">
-        <v>325</v>
+        <v>791</v>
       </c>
       <c r="H125" t="s">
-        <v>548</v>
+        <v>829</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -5910,25 +6188,25 @@
         <v>397</v>
       </c>
       <c r="B126" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C126" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D126" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="F126" t="s">
-        <v>713</v>
+        <v>285</v>
       </c>
       <c r="G126" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="H126" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -5936,25 +6214,25 @@
         <v>397</v>
       </c>
       <c r="B127" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C127" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D127" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="F127" t="s">
-        <v>737</v>
+        <v>288</v>
       </c>
       <c r="G127" t="s">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="H127" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -5962,25 +6240,25 @@
         <v>397</v>
       </c>
       <c r="B128" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C128" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D128" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="F128" t="s">
-        <v>738</v>
+        <v>291</v>
       </c>
       <c r="G128" t="s">
-        <v>331</v>
+        <v>292</v>
       </c>
       <c r="H128" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -5988,25 +6266,25 @@
         <v>397</v>
       </c>
       <c r="B129" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C129" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D129" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>332</v>
+        <v>792</v>
       </c>
       <c r="F129" t="s">
-        <v>739</v>
+        <v>793</v>
       </c>
       <c r="G129" t="s">
-        <v>333</v>
+        <v>794</v>
       </c>
       <c r="H129" t="s">
-        <v>552</v>
+        <v>830</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -6014,25 +6292,25 @@
         <v>397</v>
       </c>
       <c r="B130" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C130" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>714</v>
+        <v>795</v>
       </c>
       <c r="F130" t="s">
-        <v>740</v>
+        <v>796</v>
       </c>
       <c r="G130" t="s">
-        <v>715</v>
+        <v>797</v>
       </c>
       <c r="H130" t="s">
-        <v>720</v>
+        <v>831</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -6040,25 +6318,25 @@
         <v>397</v>
       </c>
       <c r="B131" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C131" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D131" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>716</v>
+        <v>798</v>
       </c>
       <c r="F131" t="s">
-        <v>741</v>
+        <v>799</v>
       </c>
       <c r="G131" t="s">
-        <v>717</v>
+        <v>800</v>
       </c>
       <c r="H131" t="s">
-        <v>721</v>
+        <v>832</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -6066,25 +6344,25 @@
         <v>397</v>
       </c>
       <c r="B132" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>334</v>
+        <v>293</v>
       </c>
       <c r="F132" t="s">
-        <v>335</v>
+        <v>294</v>
       </c>
       <c r="G132" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="H132" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -6092,25 +6370,25 @@
         <v>397</v>
       </c>
       <c r="B133" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>337</v>
+        <v>801</v>
       </c>
       <c r="F133" t="s">
-        <v>405</v>
+        <v>802</v>
       </c>
       <c r="G133" t="s">
-        <v>338</v>
+        <v>803</v>
       </c>
       <c r="H133" t="s">
-        <v>554</v>
+        <v>833</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -6118,25 +6396,25 @@
         <v>397</v>
       </c>
       <c r="B134" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>339</v>
+        <v>804</v>
       </c>
       <c r="F134" t="s">
-        <v>406</v>
+        <v>805</v>
       </c>
       <c r="G134" t="s">
-        <v>340</v>
+        <v>806</v>
       </c>
       <c r="H134" t="s">
-        <v>555</v>
+        <v>834</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -6144,25 +6422,25 @@
         <v>397</v>
       </c>
       <c r="B135" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C135" t="s">
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>341</v>
+        <v>807</v>
       </c>
       <c r="F135" t="s">
-        <v>407</v>
+        <v>808</v>
       </c>
       <c r="G135" t="s">
-        <v>342</v>
+        <v>809</v>
       </c>
       <c r="H135" t="s">
-        <v>556</v>
+        <v>835</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -6170,25 +6448,25 @@
         <v>397</v>
       </c>
       <c r="B136" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
       </c>
       <c r="D136" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E136" t="s">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="F136" t="s">
-        <v>408</v>
+        <v>297</v>
       </c>
       <c r="G136" t="s">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="H136" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -6196,25 +6474,25 @@
         <v>397</v>
       </c>
       <c r="B137" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="E137" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="F137" t="s">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="G137" t="s">
-        <v>347</v>
+        <v>301</v>
       </c>
       <c r="H137" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -6222,25 +6500,25 @@
         <v>397</v>
       </c>
       <c r="B138" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="E138" t="s">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="F138" t="s">
-        <v>349</v>
+        <v>303</v>
       </c>
       <c r="G138" t="s">
-        <v>350</v>
+        <v>304</v>
       </c>
       <c r="H138" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -6248,25 +6526,25 @@
         <v>397</v>
       </c>
       <c r="B139" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
       </c>
       <c r="D139" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="E139" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="F139" t="s">
-        <v>352</v>
+        <v>306</v>
       </c>
       <c r="G139" t="s">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="H139" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -6274,25 +6552,25 @@
         <v>397</v>
       </c>
       <c r="B140" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="E140" t="s">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="F140" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="G140" t="s">
-        <v>356</v>
+        <v>310</v>
       </c>
       <c r="H140" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -6300,25 +6578,25 @@
         <v>397</v>
       </c>
       <c r="B141" t="s">
-        <v>311</v>
+        <v>201</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>810</v>
       </c>
       <c r="E141" t="s">
-        <v>357</v>
+        <v>811</v>
       </c>
       <c r="F141" t="s">
-        <v>358</v>
+        <v>812</v>
       </c>
       <c r="G141" t="s">
-        <v>359</v>
+        <v>813</v>
       </c>
       <c r="H141" t="s">
-        <v>562</v>
+        <v>836</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -6329,22 +6607,22 @@
         <v>311</v>
       </c>
       <c r="C142" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D142" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="F142" t="s">
-        <v>361</v>
+        <v>732</v>
       </c>
       <c r="G142" t="s">
-        <v>362</v>
+        <v>313</v>
       </c>
       <c r="H142" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -6355,22 +6633,22 @@
         <v>311</v>
       </c>
       <c r="C143" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="F143" t="s">
-        <v>364</v>
+        <v>733</v>
       </c>
       <c r="G143" t="s">
-        <v>365</v>
+        <v>315</v>
       </c>
       <c r="H143" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -6381,22 +6659,22 @@
         <v>311</v>
       </c>
       <c r="C144" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D144" t="s">
-        <v>366</v>
+        <v>8</v>
       </c>
       <c r="E144" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="F144" t="s">
-        <v>368</v>
+        <v>705</v>
       </c>
       <c r="G144" t="s">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="H144" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -6407,22 +6685,22 @@
         <v>311</v>
       </c>
       <c r="C145" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D145" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="E145" t="s">
-        <v>370</v>
+        <v>318</v>
       </c>
       <c r="F145" t="s">
-        <v>371</v>
+        <v>706</v>
       </c>
       <c r="G145" t="s">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="H145" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -6433,22 +6711,22 @@
         <v>311</v>
       </c>
       <c r="C146" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D146" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="E146" t="s">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="F146" t="s">
-        <v>374</v>
+        <v>707</v>
       </c>
       <c r="G146" t="s">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c r="H146" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -6459,22 +6737,22 @@
         <v>311</v>
       </c>
       <c r="C147" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D147" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="E147" t="s">
-        <v>376</v>
+        <v>322</v>
       </c>
       <c r="F147" t="s">
-        <v>377</v>
+        <v>708</v>
       </c>
       <c r="G147" t="s">
-        <v>378</v>
+        <v>323</v>
       </c>
       <c r="H147" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -6482,25 +6760,25 @@
         <v>397</v>
       </c>
       <c r="B148" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="C148" t="s">
         <v>7</v>
       </c>
       <c r="D148" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
-        <v>380</v>
+        <v>324</v>
       </c>
       <c r="F148" t="s">
-        <v>742</v>
+        <v>709</v>
       </c>
       <c r="G148" t="s">
-        <v>381</v>
+        <v>325</v>
       </c>
       <c r="H148" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -6508,25 +6786,25 @@
         <v>397</v>
       </c>
       <c r="B149" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="C149" t="s">
         <v>7</v>
       </c>
       <c r="D149" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>382</v>
+        <v>326</v>
       </c>
       <c r="F149" t="s">
-        <v>743</v>
+        <v>710</v>
       </c>
       <c r="G149" t="s">
-        <v>383</v>
+        <v>327</v>
       </c>
       <c r="H149" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -6534,25 +6812,25 @@
         <v>397</v>
       </c>
       <c r="B150" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="C150" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D150" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E150" t="s">
-        <v>384</v>
+        <v>328</v>
       </c>
       <c r="F150" t="s">
-        <v>385</v>
+        <v>734</v>
       </c>
       <c r="G150" t="s">
-        <v>386</v>
+        <v>329</v>
       </c>
       <c r="H150" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -6560,25 +6838,25 @@
         <v>397</v>
       </c>
       <c r="B151" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="C151" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E151" t="s">
-        <v>387</v>
+        <v>330</v>
       </c>
       <c r="F151" t="s">
-        <v>388</v>
+        <v>735</v>
       </c>
       <c r="G151" t="s">
-        <v>389</v>
+        <v>331</v>
       </c>
       <c r="H151" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -6586,25 +6864,25 @@
         <v>397</v>
       </c>
       <c r="B152" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="C152" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D152" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="E152" t="s">
-        <v>390</v>
+        <v>332</v>
       </c>
       <c r="F152" t="s">
-        <v>391</v>
+        <v>736</v>
       </c>
       <c r="G152" t="s">
-        <v>392</v>
+        <v>333</v>
       </c>
       <c r="H152" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -6612,805 +6890,805 @@
         <v>397</v>
       </c>
       <c r="B153" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="C153" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D153" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="E153" t="s">
-        <v>393</v>
+        <v>711</v>
       </c>
       <c r="F153" t="s">
-        <v>394</v>
+        <v>737</v>
       </c>
       <c r="G153" t="s">
-        <v>395</v>
+        <v>712</v>
       </c>
       <c r="H153" t="s">
-        <v>574</v>
+        <v>717</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B154" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C154" t="s">
-        <v>411</v>
-      </c>
-      <c r="D154">
-        <v>66</v>
+        <v>10</v>
+      </c>
+      <c r="D154" t="s">
+        <v>12</v>
       </c>
       <c r="E154" t="s">
-        <v>418</v>
+        <v>713</v>
       </c>
       <c r="F154" t="s">
-        <v>418</v>
+        <v>738</v>
       </c>
       <c r="G154" t="s">
-        <v>419</v>
+        <v>714</v>
       </c>
       <c r="H154" t="s">
-        <v>575</v>
+        <v>718</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B155" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C155" t="s">
-        <v>411</v>
-      </c>
-      <c r="D155">
-        <v>66</v>
+        <v>14</v>
+      </c>
+      <c r="D155" t="s">
+        <v>15</v>
       </c>
       <c r="E155" t="s">
-        <v>414</v>
+        <v>334</v>
       </c>
       <c r="F155" t="s">
-        <v>414</v>
+        <v>335</v>
       </c>
       <c r="G155" t="s">
-        <v>415</v>
+        <v>336</v>
       </c>
       <c r="H155" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B156" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C156" t="s">
-        <v>411</v>
-      </c>
-      <c r="D156">
-        <v>66</v>
+        <v>14</v>
+      </c>
+      <c r="D156" t="s">
+        <v>16</v>
       </c>
       <c r="E156" t="s">
-        <v>416</v>
+        <v>337</v>
       </c>
       <c r="F156" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="G156" t="s">
-        <v>417</v>
+        <v>338</v>
       </c>
       <c r="H156" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B157" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C157" t="s">
-        <v>411</v>
-      </c>
-      <c r="D157">
-        <v>66</v>
+        <v>14</v>
+      </c>
+      <c r="D157" t="s">
+        <v>80</v>
       </c>
       <c r="E157" t="s">
-        <v>412</v>
+        <v>339</v>
       </c>
       <c r="F157" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="G157" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="H157" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B158" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C158" t="s">
-        <v>411</v>
-      </c>
-      <c r="D158">
-        <v>55</v>
+        <v>14</v>
+      </c>
+      <c r="D158" t="s">
+        <v>80</v>
       </c>
       <c r="E158" t="s">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="F158" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="G158" t="s">
-        <v>425</v>
+        <v>342</v>
       </c>
       <c r="H158" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B159" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C159" t="s">
-        <v>411</v>
-      </c>
-      <c r="D159">
-        <v>55</v>
+        <v>14</v>
+      </c>
+      <c r="D159" t="s">
+        <v>80</v>
       </c>
       <c r="E159" t="s">
-        <v>422</v>
+        <v>343</v>
       </c>
       <c r="F159" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="G159" t="s">
-        <v>423</v>
+        <v>344</v>
       </c>
       <c r="H159" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B160" t="s">
-        <v>410</v>
+        <v>311</v>
       </c>
       <c r="C160" t="s">
-        <v>411</v>
-      </c>
-      <c r="D160">
-        <v>55</v>
+        <v>14</v>
+      </c>
+      <c r="D160" t="s">
+        <v>17</v>
       </c>
       <c r="E160" t="s">
-        <v>420</v>
+        <v>345</v>
       </c>
       <c r="F160" t="s">
-        <v>420</v>
+        <v>346</v>
       </c>
       <c r="G160" t="s">
-        <v>421</v>
+        <v>347</v>
       </c>
       <c r="H160" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B161" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C161" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D161" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>83</v>
+        <v>348</v>
       </c>
       <c r="F161" t="s">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="G161" t="s">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="H161" t="s">
-        <v>426</v>
+        <v>559</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B162" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C162" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D162" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>86</v>
+        <v>351</v>
       </c>
       <c r="F162" t="s">
-        <v>86</v>
+        <v>352</v>
       </c>
       <c r="G162" t="s">
-        <v>87</v>
+        <v>353</v>
       </c>
       <c r="H162" t="s">
-        <v>427</v>
+        <v>560</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B163" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C163" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D163" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>88</v>
+        <v>354</v>
       </c>
       <c r="F163" t="s">
-        <v>88</v>
+        <v>355</v>
       </c>
       <c r="G163" t="s">
-        <v>87</v>
+        <v>356</v>
       </c>
       <c r="H163" t="s">
-        <v>428</v>
+        <v>561</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B164" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C164" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D164" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>89</v>
+        <v>357</v>
       </c>
       <c r="F164" t="s">
-        <v>89</v>
+        <v>358</v>
       </c>
       <c r="G164" t="s">
-        <v>90</v>
+        <v>359</v>
       </c>
       <c r="H164" t="s">
-        <v>429</v>
+        <v>562</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B165" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C165" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>92</v>
+        <v>360</v>
       </c>
       <c r="F165" t="s">
-        <v>92</v>
+        <v>361</v>
       </c>
       <c r="G165" t="s">
-        <v>93</v>
+        <v>362</v>
       </c>
       <c r="H165" t="s">
-        <v>430</v>
+        <v>563</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B166" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C166" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D166" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>95</v>
+        <v>363</v>
       </c>
       <c r="F166" t="s">
-        <v>95</v>
+        <v>364</v>
       </c>
       <c r="G166" t="s">
-        <v>96</v>
+        <v>365</v>
       </c>
       <c r="H166" t="s">
-        <v>431</v>
+        <v>564</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B167" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C167" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D167" t="s">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="E167" t="s">
-        <v>97</v>
+        <v>367</v>
       </c>
       <c r="F167" t="s">
-        <v>97</v>
+        <v>368</v>
       </c>
       <c r="G167" t="s">
-        <v>98</v>
+        <v>369</v>
       </c>
       <c r="H167" t="s">
-        <v>432</v>
+        <v>565</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B168" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C168" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D168" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E168" t="s">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="F168" t="s">
-        <v>99</v>
+        <v>371</v>
       </c>
       <c r="G168" t="s">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="H168" t="s">
-        <v>433</v>
+        <v>566</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B169" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C169" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D169" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E169" t="s">
-        <v>101</v>
+        <v>373</v>
       </c>
       <c r="F169" t="s">
-        <v>101</v>
+        <v>374</v>
       </c>
       <c r="G169" t="s">
-        <v>102</v>
+        <v>375</v>
       </c>
       <c r="H169" t="s">
-        <v>434</v>
+        <v>567</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B170" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="C170" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D170" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E170" t="s">
-        <v>103</v>
+        <v>376</v>
       </c>
       <c r="F170" t="s">
-        <v>103</v>
+        <v>377</v>
       </c>
       <c r="G170" t="s">
-        <v>104</v>
+        <v>378</v>
       </c>
       <c r="H170" t="s">
-        <v>435</v>
+        <v>568</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B171" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="C171" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="D171" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="E171" t="s">
-        <v>105</v>
+        <v>380</v>
       </c>
       <c r="F171" t="s">
-        <v>105</v>
+        <v>739</v>
       </c>
       <c r="G171" t="s">
-        <v>106</v>
+        <v>381</v>
       </c>
       <c r="H171" t="s">
-        <v>436</v>
+        <v>569</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B172" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="C172" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="D172" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E172" t="s">
-        <v>108</v>
+        <v>382</v>
       </c>
       <c r="F172" t="s">
-        <v>108</v>
+        <v>740</v>
       </c>
       <c r="G172" t="s">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="H172" t="s">
-        <v>437</v>
+        <v>570</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B173" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="C173" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="D173" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="E173" t="s">
-        <v>109</v>
+        <v>384</v>
       </c>
       <c r="F173" t="s">
-        <v>109</v>
+        <v>385</v>
       </c>
       <c r="G173" t="s">
-        <v>87</v>
+        <v>386</v>
       </c>
       <c r="H173" t="s">
-        <v>438</v>
+        <v>571</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B174" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="C174" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="D174" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="E174" t="s">
-        <v>110</v>
+        <v>387</v>
       </c>
       <c r="F174" t="s">
-        <v>110</v>
+        <v>388</v>
       </c>
       <c r="G174" t="s">
-        <v>111</v>
+        <v>389</v>
       </c>
       <c r="H174" t="s">
-        <v>439</v>
+        <v>572</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B175" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="C175" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D175" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E175" t="s">
-        <v>113</v>
+        <v>390</v>
       </c>
       <c r="F175" t="s">
-        <v>113</v>
+        <v>391</v>
       </c>
       <c r="G175" t="s">
-        <v>96</v>
+        <v>392</v>
       </c>
       <c r="H175" t="s">
-        <v>440</v>
+        <v>573</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>590</v>
+        <v>397</v>
       </c>
       <c r="B176" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="C176" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="D176" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="E176" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
       <c r="F176" t="s">
-        <v>114</v>
+        <v>394</v>
       </c>
       <c r="G176" t="s">
-        <v>100</v>
+        <v>395</v>
       </c>
       <c r="H176" t="s">
-        <v>441</v>
+        <v>574</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B177" t="s">
+        <v>410</v>
+      </c>
+      <c r="C177" t="s">
         <v>411</v>
       </c>
-      <c r="C177" t="s">
-        <v>112</v>
-      </c>
-      <c r="D177" t="s">
-        <v>91</v>
+      <c r="D177">
+        <v>66</v>
       </c>
       <c r="E177" t="s">
-        <v>115</v>
+        <v>418</v>
       </c>
       <c r="F177" t="s">
-        <v>115</v>
+        <v>418</v>
       </c>
       <c r="G177" t="s">
-        <v>116</v>
+        <v>419</v>
       </c>
       <c r="H177" t="s">
-        <v>442</v>
+        <v>575</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B178" t="s">
+        <v>410</v>
+      </c>
+      <c r="C178" t="s">
         <v>411</v>
       </c>
-      <c r="C178" t="s">
-        <v>112</v>
-      </c>
-      <c r="D178" t="s">
-        <v>91</v>
+      <c r="D178">
+        <v>66</v>
       </c>
       <c r="E178" t="s">
-        <v>117</v>
+        <v>414</v>
       </c>
       <c r="F178" t="s">
-        <v>117</v>
+        <v>414</v>
       </c>
       <c r="G178" t="s">
-        <v>118</v>
+        <v>415</v>
       </c>
       <c r="H178" t="s">
-        <v>443</v>
+        <v>575</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B179" t="s">
+        <v>410</v>
+      </c>
+      <c r="C179" t="s">
         <v>411</v>
       </c>
-      <c r="C179" t="s">
-        <v>119</v>
-      </c>
-      <c r="D179" t="s">
-        <v>82</v>
+      <c r="D179">
+        <v>66</v>
       </c>
       <c r="E179" t="s">
-        <v>120</v>
+        <v>416</v>
       </c>
       <c r="F179" t="s">
-        <v>120</v>
+        <v>416</v>
       </c>
       <c r="G179" t="s">
-        <v>121</v>
+        <v>417</v>
       </c>
       <c r="H179" t="s">
-        <v>444</v>
+        <v>575</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B180" t="s">
+        <v>410</v>
+      </c>
+      <c r="C180" t="s">
         <v>411</v>
       </c>
-      <c r="C180" t="s">
-        <v>119</v>
-      </c>
-      <c r="D180" t="s">
-        <v>85</v>
+      <c r="D180">
+        <v>66</v>
       </c>
       <c r="E180" t="s">
-        <v>122</v>
+        <v>412</v>
       </c>
       <c r="F180" t="s">
-        <v>122</v>
+        <v>412</v>
       </c>
       <c r="G180" t="s">
-        <v>123</v>
+        <v>413</v>
       </c>
       <c r="H180" t="s">
-        <v>445</v>
+        <v>575</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B181" t="s">
+        <v>410</v>
+      </c>
+      <c r="C181" t="s">
         <v>411</v>
       </c>
-      <c r="C181" t="s">
-        <v>119</v>
-      </c>
-      <c r="D181" t="s">
-        <v>85</v>
+      <c r="D181">
+        <v>55</v>
       </c>
       <c r="E181" t="s">
-        <v>124</v>
+        <v>424</v>
       </c>
       <c r="F181" t="s">
-        <v>124</v>
+        <v>424</v>
       </c>
       <c r="G181" t="s">
-        <v>125</v>
+        <v>425</v>
       </c>
       <c r="H181" t="s">
-        <v>446</v>
+        <v>576</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B182" t="s">
+        <v>410</v>
+      </c>
+      <c r="C182" t="s">
         <v>411</v>
       </c>
-      <c r="C182" t="s">
-        <v>119</v>
-      </c>
-      <c r="D182" t="s">
-        <v>85</v>
+      <c r="D182">
+        <v>55</v>
       </c>
       <c r="E182" t="s">
-        <v>126</v>
+        <v>422</v>
       </c>
       <c r="F182" t="s">
-        <v>126</v>
+        <v>422</v>
       </c>
       <c r="G182" t="s">
-        <v>127</v>
+        <v>423</v>
       </c>
       <c r="H182" t="s">
-        <v>447</v>
+        <v>576</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B183" t="s">
+        <v>410</v>
+      </c>
+      <c r="C183" t="s">
         <v>411</v>
       </c>
-      <c r="C183" t="s">
-        <v>119</v>
-      </c>
-      <c r="D183" t="s">
-        <v>91</v>
+      <c r="D183">
+        <v>55</v>
       </c>
       <c r="E183" t="s">
-        <v>128</v>
+        <v>420</v>
       </c>
       <c r="F183" t="s">
-        <v>128</v>
+        <v>420</v>
       </c>
       <c r="G183" t="s">
-        <v>129</v>
+        <v>421</v>
       </c>
       <c r="H183" t="s">
-        <v>448</v>
+        <v>576</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -7421,22 +7699,22 @@
         <v>411</v>
       </c>
       <c r="C184" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="D184" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E184" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="F184" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="G184" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="H184" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -7447,21 +7725,619 @@
         <v>411</v>
       </c>
       <c r="C185" t="s">
+        <v>81</v>
+      </c>
+      <c r="D185" t="s">
+        <v>85</v>
+      </c>
+      <c r="E185" t="s">
+        <v>86</v>
+      </c>
+      <c r="F185" t="s">
+        <v>86</v>
+      </c>
+      <c r="G185" t="s">
+        <v>87</v>
+      </c>
+      <c r="H185" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>590</v>
+      </c>
+      <c r="B186" t="s">
+        <v>411</v>
+      </c>
+      <c r="C186" t="s">
+        <v>81</v>
+      </c>
+      <c r="D186" t="s">
+        <v>85</v>
+      </c>
+      <c r="E186" t="s">
+        <v>88</v>
+      </c>
+      <c r="F186" t="s">
+        <v>88</v>
+      </c>
+      <c r="G186" t="s">
+        <v>87</v>
+      </c>
+      <c r="H186" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>590</v>
+      </c>
+      <c r="B187" t="s">
+        <v>411</v>
+      </c>
+      <c r="C187" t="s">
+        <v>81</v>
+      </c>
+      <c r="D187" t="s">
+        <v>85</v>
+      </c>
+      <c r="E187" t="s">
+        <v>89</v>
+      </c>
+      <c r="F187" t="s">
+        <v>89</v>
+      </c>
+      <c r="G187" t="s">
+        <v>90</v>
+      </c>
+      <c r="H187" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>590</v>
+      </c>
+      <c r="B188" t="s">
+        <v>411</v>
+      </c>
+      <c r="C188" t="s">
+        <v>81</v>
+      </c>
+      <c r="D188" t="s">
+        <v>91</v>
+      </c>
+      <c r="E188" t="s">
+        <v>92</v>
+      </c>
+      <c r="F188" t="s">
+        <v>92</v>
+      </c>
+      <c r="G188" t="s">
+        <v>93</v>
+      </c>
+      <c r="H188" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>590</v>
+      </c>
+      <c r="B189" t="s">
+        <v>411</v>
+      </c>
+      <c r="C189" t="s">
+        <v>94</v>
+      </c>
+      <c r="D189" t="s">
+        <v>82</v>
+      </c>
+      <c r="E189" t="s">
+        <v>95</v>
+      </c>
+      <c r="F189" t="s">
+        <v>95</v>
+      </c>
+      <c r="G189" t="s">
+        <v>96</v>
+      </c>
+      <c r="H189" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>590</v>
+      </c>
+      <c r="B190" t="s">
+        <v>411</v>
+      </c>
+      <c r="C190" t="s">
+        <v>94</v>
+      </c>
+      <c r="D190" t="s">
+        <v>82</v>
+      </c>
+      <c r="E190" t="s">
+        <v>97</v>
+      </c>
+      <c r="F190" t="s">
+        <v>97</v>
+      </c>
+      <c r="G190" t="s">
+        <v>98</v>
+      </c>
+      <c r="H190" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>590</v>
+      </c>
+      <c r="B191" t="s">
+        <v>411</v>
+      </c>
+      <c r="C191" t="s">
+        <v>94</v>
+      </c>
+      <c r="D191" t="s">
+        <v>85</v>
+      </c>
+      <c r="E191" t="s">
+        <v>99</v>
+      </c>
+      <c r="F191" t="s">
+        <v>99</v>
+      </c>
+      <c r="G191" t="s">
+        <v>100</v>
+      </c>
+      <c r="H191" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>590</v>
+      </c>
+      <c r="B192" t="s">
+        <v>411</v>
+      </c>
+      <c r="C192" t="s">
+        <v>94</v>
+      </c>
+      <c r="D192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E192" t="s">
+        <v>101</v>
+      </c>
+      <c r="F192" t="s">
+        <v>101</v>
+      </c>
+      <c r="G192" t="s">
+        <v>102</v>
+      </c>
+      <c r="H192" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>590</v>
+      </c>
+      <c r="B193" t="s">
+        <v>411</v>
+      </c>
+      <c r="C193" t="s">
+        <v>94</v>
+      </c>
+      <c r="D193" t="s">
+        <v>91</v>
+      </c>
+      <c r="E193" t="s">
+        <v>103</v>
+      </c>
+      <c r="F193" t="s">
+        <v>103</v>
+      </c>
+      <c r="G193" t="s">
+        <v>104</v>
+      </c>
+      <c r="H193" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>590</v>
+      </c>
+      <c r="B194" t="s">
+        <v>411</v>
+      </c>
+      <c r="C194" t="s">
+        <v>94</v>
+      </c>
+      <c r="D194" t="s">
+        <v>91</v>
+      </c>
+      <c r="E194" t="s">
+        <v>105</v>
+      </c>
+      <c r="F194" t="s">
+        <v>105</v>
+      </c>
+      <c r="G194" t="s">
+        <v>106</v>
+      </c>
+      <c r="H194" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>590</v>
+      </c>
+      <c r="B195" t="s">
+        <v>411</v>
+      </c>
+      <c r="C195" t="s">
+        <v>107</v>
+      </c>
+      <c r="D195" t="s">
+        <v>82</v>
+      </c>
+      <c r="E195" t="s">
+        <v>108</v>
+      </c>
+      <c r="F195" t="s">
+        <v>108</v>
+      </c>
+      <c r="G195" t="s">
+        <v>84</v>
+      </c>
+      <c r="H195" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>590</v>
+      </c>
+      <c r="B196" t="s">
+        <v>411</v>
+      </c>
+      <c r="C196" t="s">
+        <v>107</v>
+      </c>
+      <c r="D196" t="s">
+        <v>85</v>
+      </c>
+      <c r="E196" t="s">
+        <v>109</v>
+      </c>
+      <c r="F196" t="s">
+        <v>109</v>
+      </c>
+      <c r="G196" t="s">
+        <v>87</v>
+      </c>
+      <c r="H196" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>590</v>
+      </c>
+      <c r="B197" t="s">
+        <v>411</v>
+      </c>
+      <c r="C197" t="s">
+        <v>107</v>
+      </c>
+      <c r="D197" t="s">
+        <v>91</v>
+      </c>
+      <c r="E197" t="s">
+        <v>110</v>
+      </c>
+      <c r="F197" t="s">
+        <v>110</v>
+      </c>
+      <c r="G197" t="s">
+        <v>111</v>
+      </c>
+      <c r="H197" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>590</v>
+      </c>
+      <c r="B198" t="s">
+        <v>411</v>
+      </c>
+      <c r="C198" t="s">
+        <v>112</v>
+      </c>
+      <c r="D198" t="s">
+        <v>82</v>
+      </c>
+      <c r="E198" t="s">
+        <v>113</v>
+      </c>
+      <c r="F198" t="s">
+        <v>113</v>
+      </c>
+      <c r="G198" t="s">
+        <v>96</v>
+      </c>
+      <c r="H198" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>590</v>
+      </c>
+      <c r="B199" t="s">
+        <v>411</v>
+      </c>
+      <c r="C199" t="s">
+        <v>112</v>
+      </c>
+      <c r="D199" t="s">
+        <v>85</v>
+      </c>
+      <c r="E199" t="s">
+        <v>114</v>
+      </c>
+      <c r="F199" t="s">
+        <v>114</v>
+      </c>
+      <c r="G199" t="s">
+        <v>100</v>
+      </c>
+      <c r="H199" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>590</v>
+      </c>
+      <c r="B200" t="s">
+        <v>411</v>
+      </c>
+      <c r="C200" t="s">
+        <v>112</v>
+      </c>
+      <c r="D200" t="s">
+        <v>91</v>
+      </c>
+      <c r="E200" t="s">
+        <v>115</v>
+      </c>
+      <c r="F200" t="s">
+        <v>115</v>
+      </c>
+      <c r="G200" t="s">
+        <v>116</v>
+      </c>
+      <c r="H200" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>590</v>
+      </c>
+      <c r="B201" t="s">
+        <v>411</v>
+      </c>
+      <c r="C201" t="s">
+        <v>112</v>
+      </c>
+      <c r="D201" t="s">
+        <v>91</v>
+      </c>
+      <c r="E201" t="s">
+        <v>117</v>
+      </c>
+      <c r="F201" t="s">
+        <v>117</v>
+      </c>
+      <c r="G201" t="s">
+        <v>118</v>
+      </c>
+      <c r="H201" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>590</v>
+      </c>
+      <c r="B202" t="s">
+        <v>411</v>
+      </c>
+      <c r="C202" t="s">
         <v>119</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D202" t="s">
+        <v>82</v>
+      </c>
+      <c r="E202" t="s">
+        <v>120</v>
+      </c>
+      <c r="F202" t="s">
+        <v>120</v>
+      </c>
+      <c r="G202" t="s">
+        <v>121</v>
+      </c>
+      <c r="H202" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>590</v>
+      </c>
+      <c r="B203" t="s">
+        <v>411</v>
+      </c>
+      <c r="C203" t="s">
+        <v>119</v>
+      </c>
+      <c r="D203" t="s">
+        <v>85</v>
+      </c>
+      <c r="E203" t="s">
+        <v>122</v>
+      </c>
+      <c r="F203" t="s">
+        <v>122</v>
+      </c>
+      <c r="G203" t="s">
+        <v>123</v>
+      </c>
+      <c r="H203" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>590</v>
+      </c>
+      <c r="B204" t="s">
+        <v>411</v>
+      </c>
+      <c r="C204" t="s">
+        <v>119</v>
+      </c>
+      <c r="D204" t="s">
+        <v>85</v>
+      </c>
+      <c r="E204" t="s">
+        <v>124</v>
+      </c>
+      <c r="F204" t="s">
+        <v>124</v>
+      </c>
+      <c r="G204" t="s">
+        <v>125</v>
+      </c>
+      <c r="H204" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>590</v>
+      </c>
+      <c r="B205" t="s">
+        <v>411</v>
+      </c>
+      <c r="C205" t="s">
+        <v>119</v>
+      </c>
+      <c r="D205" t="s">
+        <v>85</v>
+      </c>
+      <c r="E205" t="s">
+        <v>126</v>
+      </c>
+      <c r="F205" t="s">
+        <v>126</v>
+      </c>
+      <c r="G205" t="s">
+        <v>127</v>
+      </c>
+      <c r="H205" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>590</v>
+      </c>
+      <c r="B206" t="s">
+        <v>411</v>
+      </c>
+      <c r="C206" t="s">
+        <v>119</v>
+      </c>
+      <c r="D206" t="s">
         <v>91</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E206" t="s">
+        <v>128</v>
+      </c>
+      <c r="F206" t="s">
+        <v>128</v>
+      </c>
+      <c r="G206" t="s">
+        <v>129</v>
+      </c>
+      <c r="H206" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>590</v>
+      </c>
+      <c r="B207" t="s">
+        <v>411</v>
+      </c>
+      <c r="C207" t="s">
+        <v>119</v>
+      </c>
+      <c r="D207" t="s">
+        <v>91</v>
+      </c>
+      <c r="E207" t="s">
+        <v>130</v>
+      </c>
+      <c r="F207" t="s">
+        <v>130</v>
+      </c>
+      <c r="G207" t="s">
+        <v>131</v>
+      </c>
+      <c r="H207" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>590</v>
+      </c>
+      <c r="B208" t="s">
+        <v>411</v>
+      </c>
+      <c r="C208" t="s">
+        <v>119</v>
+      </c>
+      <c r="D208" t="s">
+        <v>91</v>
+      </c>
+      <c r="E208" t="s">
         <v>132</v>
       </c>
-      <c r="F185" t="s">
+      <c r="F208" t="s">
         <v>132</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G208" t="s">
         <v>133</v>
       </c>
-      <c r="H185" t="s">
+      <c r="H208" t="s">
         <v>450</v>
       </c>
     </row>
